--- a/www/download/COUNTRY.SVN.EXI382.xlsx
+++ b/www/download/COUNTRY.SVN.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>Eslovênia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42603926380368</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42603926380368</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42603926380368</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42603926380368</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42603926380368</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42603926380368</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42603926380368</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42603926380368</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42603926380368</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42603926380368</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42603926380368</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42557300613497</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42557300613497</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42557300613497</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42557300613497</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42557300613497</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42557300613497</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42557300613497</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42557300613497</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42557300613497</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42557300613497</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42557300613497</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42557300613497</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42557300613497</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42557300613497</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42557300613497</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42557300613497</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1.134</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.909</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.927</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.913</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.919</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.935</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.946</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.965</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.974</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0.986</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>1.006</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0.991</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0.975</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.962</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0.932</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0.919</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0.906</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0.928</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0.956</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>1.017</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>1.055</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>1.117</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0.913</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.759</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.751</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.753</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.751</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.746</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.776</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.795</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.795</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.817</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.851</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0.851</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0.817</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0.796</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0.775</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0.769</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.755</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0.739</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0.766</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>0.757</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>0.824</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>0.908</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2232.146</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2018.98</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1996.752</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1956.224</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1979.159</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1982.423</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1976.89</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1969.298</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2009.123</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1937.166</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2020.152</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2062.407</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2053.903</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2105.927</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>2066.279</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1999.6</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>1959.744</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1885.166</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1865.533</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1831.86</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>1796.069</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>1867.298</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>1845.664</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>1915.773</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2034.112</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>2103.568</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2220.648</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1487.721</t>
+          <t>2978256834.72669</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1237.153</t>
+          <t>3301321244.30366</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1224.756</t>
+          <t>2858313212.13252</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1149.186</t>
+          <t>2676123810.49865</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1116.763</t>
+          <t>2811098657.47884</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1152.637</t>
+          <t>2804089332.62444</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1266.666</t>
+          <t>2801748125.13946</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1206.75</t>
+          <t>2768685096.5985</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1277.217</t>
+          <t>2797698348.82986</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1332.742</t>
+          <t>2822129394.60027</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1349.86</t>
+          <t>3076676745.30912</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1418.119</t>
+          <t>3295297939.60543</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1381.085</t>
+          <t>3160142600.12633</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1422.379</t>
+          <t>3309332116.03187</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1059.615</t>
+          <t>2870564019.47026</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>969.944</t>
+          <t>2851953220.23997</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>921.764</t>
+          <t>2999833425.81043</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>938.904</t>
+          <t>2829637637.35225</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>943.439</t>
+          <t>2837907718.12603</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1363.228</t>
+          <t>2649308558.26144</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>1325.301</t>
+          <t>2528789678.58411</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>1365.311</t>
+          <t>2785843048.68369</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1333.555</t>
+          <t>2916557424.80758</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1379.206</t>
+          <t>3147932828.65583</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1429.648</t>
+          <t>3181948409.78592</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>1476.889</t>
+          <t>3492636628.14916</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>1536.762</t>
+          <t>3131556345.27478</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1120119670.75844</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1214360051.96188</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>986376547.672545</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1115549565.23186</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1166273030.52094</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1248421760.19941</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1323434411.12695</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1132683171.34755</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1221238476.38239</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1331915342.09457</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1332312815.69784</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1396622425.87953</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1219086830.54244</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1254340277.08518</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1365306701.8318</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1440058712.1211</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1326916938.26805</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1491184780.57201</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1330194551.92767</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1162581654.72328</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>1357797439.88213</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1201364634.31255</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1298806718.52191</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>1491119185.34379</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1398898190.05756</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>1887150254.80912</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1538863832.23386</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>21128434.8784141</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>16720713.4762495</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>13630578.1710289</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>19226604.3421963</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>11283285.8305409</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>10551783.4081635</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15585778.371958</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>11505739.5028496</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>10065541.9688229</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>9756554.87361148</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>9652471.54589023</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>9581534.64372102</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>9041835.3902223</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>16438083721.3653</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>8257244.62477351</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>39087940.0126098</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>55586817859.9794</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>7177753.50244561</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>5663555.80077387</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1612803897.7477</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>1646353696.03114</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2616867466713.89</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>107186433.626755</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>1863842785.96276</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>1924208245.50973</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>2062306400.11405</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2137865251.43259</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5032.49500152948</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>10939.7580504232</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>11684.9330095595</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>11685.1138051102</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>12194.9534058101</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>14241.0275183889</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>13950.6004861404</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>13831.3514099932</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>12868.0539341058</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>11790.0569129439</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>13131.7205549405</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>14492.3322941983</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>14879.0795475053</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>15420.6173081119</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>14919.3616430659</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>16175.5764015647</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>16377.0179185771</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>17312.5331948475</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>16559.2884760979</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>17057.1591568148</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>18699.8498116056</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>17053.054611902</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>18409.0191036477</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18381.8108048778</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>21361.4795935332</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>20531.7968990677</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>21320.4803606758</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>11101.7580443013</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>25086.9792489313</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>23657.1837849332</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>22770.979668108</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>25230.4392934652</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>30084.5514015483</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30182.5362674138</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>28912.3726272362</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>26837.7091066376</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>26455.831286663</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>30919.8991207114</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>35425.4740682006</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>35197.3906594928</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>37036.4219101242</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>32193.8034856195</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>36885.3369475343</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>40390.6895011497</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>42052.2327994511</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>41197.8474541341</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>39809.1431518931</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>42924.0480876268</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>43100.9973659018</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>47706.3941804008</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>50078.7467910405</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>53933.6142356502</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>56316.8691945931</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>49574.6042776208</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.328180671873104</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.0187695140348094</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.241671857354976</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.030152344473209</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.0424514922536927</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.0767246801152397</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.0428947673184669</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.0653905968819799</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.0458375040587218</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.000620653490045253</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.0131704687487015</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.0153918294040363</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.132884849051712</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.133965819311076</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-0.223899656701287</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.326455239751045</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-0.305334061676207</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-0.370363745504386</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-0.290751117095773</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.172587121083392</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-0.0239335299671108</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.136467038106787</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.0267538963684335</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>-0.0750530539436948</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.0219814390152915</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>-0.217397051794384</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>-0.00136590379785306</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1226.58026556742</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1600.36907216911</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1313.41750688757</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1482.06398994518</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1553.16690707212</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1672.59078268922</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1705.89637938501</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1452.5303556648</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1536.34227749705</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1675.15449892403</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1631.33686261517</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1682.88037821365</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1468.60237386131</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1474.48016584577</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1603.97873805419</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1762.83353179247</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1667.60957429645</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1925.3515565807</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1729.09729874905</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1539.13470246459</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1837.70968867839</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1568.87710317382</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1715.28381878291</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1887.05655465219</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1697.86013383441</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>2195.26336248267</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1695.64323709787</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>950562249.910792</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1262862608.03095</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>780332600.997303</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>861648474.240743</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>899743445.140424</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1005410703.27387</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>945363284.260651</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>964116764.801227</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1033195346.89418</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>1131212355.86805</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>1263334909.51036</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1395896196.29691</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1155110399.01063</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1295725083.51025</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1282553602.17341</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1349643457.66656</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1427613464.21929</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1598486663.87082</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1546690331.70863</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1407793131.90163</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1441291932.50606</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1660852972.57422</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>1739198374.1754</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>2036209561.19788</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>2047637853.11414</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>2283032661.11834</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1676278419.77285</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>661647175.786118</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1238179343.07289</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>762268261.041644</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>858953172.187401</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>911913809.326344</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1047290621.58998</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>943733991.517034</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>973515844.962198</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1093663800.69116</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1188524692.36872</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1294967134.45591</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1389587188.63734</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1131999892.54161</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>1255872029.17959</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1249514335.22598</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1283054370.63084</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1359240738.11348</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1518571826.68624</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>1454881501.83439</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1312062354.79892</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>1335024040.75774</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>1556551805.41072</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>1598884938.10465</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>1859708915.11108</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>1884311450.40711</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>2087145529.07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2554392102.89449</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>288915074.124674</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>24683264.9580593</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>18064339.9556583</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2695302.05334217</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12170364.1859198</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-41879918.3161083</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1629292.74361739</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-9399080.16097089</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-60468453.7969801</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-57312336.5006689</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-31632224.9455498</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>6309007.65957591</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>23110506.4690224</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>39853054.3306642</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>33039266.9474294</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>66589087.0357165</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>68372726.1058046</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>79914837.1845803</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>91808829.8742338</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>95730777.1027122</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>106267891.748321</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>104301167.163494</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>140313436.070753</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>176500646.086809</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>163326402.70703</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>195887132.048339</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-878113683.12164</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>1629.12020122762</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>1630.40722193006</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>1630.83355525963</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>1526.75169390135</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1487.23265414785</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>1544.26178992369</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>1632.72235112187</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>1547.51218261092</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1606.76437287741</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>1676.19418941015</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1652.82233378285</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>1708.78298590252</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1663.75737862886</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>1672.01010932123</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>1244.84844924769</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1187.34728852998</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>1158.43156968639</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>1212.27114267277</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>1226.36032757048</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>1804.76952972249</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>1793.72680877355</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>1782.97711459751</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>1761.17434431308</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>1745.42719726107</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>1735.18154282279</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>1718.01957956671</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>1693.32715156051</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1969.1522038118</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2220.36731551808</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2219.10646810429</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2125.63729218693</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>2134.55457290687</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>2172.04229210011</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>2150.89761723459</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>2105.75064157404</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>2123.80866807619</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>2104.70013037794</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>2092.33764888672</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>2117.89587184247</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>2083.2772086417</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>2093.57490804205</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>2084.20314706451</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>2050.66147061877</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>2036.73248804739</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>2023.79602791195</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>2030.18065077793</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>2022.69575508857</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>2018.68185698273</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>2011.44765791836</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>2006.97935726203</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>2003.70008818681</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>1999.31729804261</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>1993.44510151103</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1987.22912837738</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>8355.12112444888</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8857.87027178221</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>10002.9220481191</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>10794.5795688117</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>10841.1897268215</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>12941.4284079602</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>14305.2889998986</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>15402.9794627327</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>15485.4199831079</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>17504.6540932809</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>19225.2570561139</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>20939.8465329299</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>22634.4764355473</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>23770.9909830708</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>19651.100374348</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>21254.2864991382</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>26677.3085193368</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>28648.3377667408</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>28854.5885251518</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>28966.9765287443</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>31665.1373913042</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>33131.7634713515</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>37562.2853784653</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>40181.9676656972</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>42322.4850761776</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>45056.8533444963</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>46078.6543769413</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>620057660.455409</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>988465322.788024</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>820118047.191892</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>745865760.126775</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>763893583.947065</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>834929031.681708</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>865672623.959368</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>883189634.693756</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>856489027.932393</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>934277443.770162</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1070637444.10026</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1169078818.93643</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1048328630.55266</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1071468344.27749</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>876392712.704043</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>934582063.423247</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1192874678.01014</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1165945072.66318</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1188860723.22499</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1102609703.97086</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>1036836199.40095</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>1204338879.77802</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>1366098220.13982</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>1486101757.23594</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1495680991.62301</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>1693960983.8245</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1415399721.17977</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>8833.73935511331</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>9134.24094128519</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>10275.4030237574</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>11231.6823932723</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>12047.9395701687</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>13998.1854027579</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>14622.6324492471</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>15080.9611501867</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>15594.1981826792</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>18028.290008756</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>19468.8945079046</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>20959.5725733569</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>23243.3573021985</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>24810.9814341429</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>18986.7030446395</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>20751.4654738845</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>26088.4853976293</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>27036.5984931873</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>26625.2849416098</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>25646.8268004135</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>27600.4227090817</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>28617.9425438445</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>32513.4908228424</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>35089.7865112797</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>36968.3509481036</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>39736.6067698372</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>41028.6384419494</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2232.146</t>
+          <t>1841769696.83562</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2018.98</t>
+          <t>2307469329.37203</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1996.752</t>
+          <t>1651455739.99572</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1956.224</t>
+          <t>1689863672.39329</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1979.159</t>
+          <t>1885007918.05479</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1982.423</t>
+          <t>2004285626.33664</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1976.89</t>
+          <t>1862216738.75648</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1969.298</t>
+          <t>1793421931.85075</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2009.123</t>
+          <t>1908163360.51258</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1937.166</t>
+          <t>2161519307.25928</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2020.152</t>
+          <t>2374720859.78405</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2062.407</t>
+          <t>2567910086.31474</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2053.903</t>
+          <t>2279051319.34463</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2105.927</t>
+          <t>2509713042.63391</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2066.279</t>
+          <t>2061152735.12782</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1999.6</t>
+          <t>2222226674.79537</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1959.744</t>
+          <t>2552587559.20751</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1885.166</t>
+          <t>2588701818.60909</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1865.533</t>
+          <t>2480176400.2339</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1831.86</t>
+          <t>2157450691.60073</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>1796.069</t>
+          <t>2085212961.0867</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>1867.298</t>
+          <t>2386471659.88084</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>1845.664</t>
+          <t>2618982783.07459</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>1915.773</t>
+          <t>3016200929.80875</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2034.112</t>
+          <t>3054660910.96934</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2103.568</t>
+          <t>3460709860.41834</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2220.648</t>
+          <t>2599629464.6966</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1487.721</t>
+          <t>-478.61823066443</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1237.153</t>
+          <t>-276.37066950298</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1224.756</t>
+          <t>-272.480975638314</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1149.186</t>
+          <t>-437.102824460597</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1116.763</t>
+          <t>-1206.74984334715</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1152.637</t>
+          <t>-1056.75699479774</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1266.666</t>
+          <t>-317.343449348428</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1206.75</t>
+          <t>322.018312546047</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1277.217</t>
+          <t>-108.778199571247</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1332.742</t>
+          <t>-523.635915475148</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1349.86</t>
+          <t>-243.637451790708</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1418.119</t>
+          <t>-19.7260404269813</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1381.085</t>
+          <t>-608.880866651245</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1422.379</t>
+          <t>-1039.99045107206</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1059.615</t>
+          <t>664.397329708493</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>969.944</t>
+          <t>502.821025253719</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>921.764</t>
+          <t>588.823121707493</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>938.904</t>
+          <t>1611.73927355355</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>943.439</t>
+          <t>2229.30358354208</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1363.228</t>
+          <t>3320.14972833086</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>1325.301</t>
+          <t>4064.71468222248</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>1365.311</t>
+          <t>4513.82092750694</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>1333.555</t>
+          <t>5048.79455562293</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>1379.206</t>
+          <t>5092.1811544175</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>1429.648</t>
+          <t>5354.13412807403</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>1476.889</t>
+          <t>5320.24657465911</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>1536.762</t>
+          <t>5050.01593499191</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3007.561</t>
+          <t>-1221712036.38021</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3260.111</t>
+          <t>-1319004006.58401</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2903.243</t>
+          <t>-831337692.803823</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2736.409</t>
+          <t>-943997912.266511</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2844.572</t>
+          <t>-1121114334.10772</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2832.385</t>
+          <t>-1169356594.65493</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2835.202</t>
+          <t>-996544114.797117</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2812.893</t>
+          <t>-910232297.156999</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2852.065</t>
+          <t>-1051674332.58019</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2834.32</t>
+          <t>-1227241863.48912</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3060.266</t>
+          <t>-1304083415.68379</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3245.293</t>
+          <t>-1398831267.3783</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>3128.756</t>
+          <t>-1230722688.79198</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3295.296</t>
+          <t>-1438244698.35642</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2912.744</t>
+          <t>-1184760022.42377</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2847.413</t>
+          <t>-1287644611.37213</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2929.234</t>
+          <t>-1359712881.19737</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2786.415</t>
+          <t>-1422756745.94591</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2781.246</t>
+          <t>-1291315677.0089</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2616.722</t>
+          <t>-1054840987.62987</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>2497.865</t>
+          <t>-1048376761.68574</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2711.566</t>
+          <t>-1182132780.10281</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2828.563</t>
+          <t>-1252884562.93477</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>3012.898</t>
+          <t>-1530099172.57281</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>3118.386</t>
+          <t>-1558979919.34632</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>3342.072</t>
+          <t>-1766748876.59384</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>3078.252</t>
+          <t>-1184229743.51682</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9604.80969141443</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>10090.5777253855</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>10595.7823549484</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>11251.9586282721</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>11939.8641446192</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>11627.4594585007</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>13765.4084129985</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>13943.2281972302</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>14351.1153546402</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>15203.7005768493</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>15607.0498125716</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>16371.9411392707</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>18079.5216688353</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>19008.455649807</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>18804.5426003164</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>19320.1979972597</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>19798.0309527001</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>19234.6636044376</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>19956.3749538041</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>20094.1034242563</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>18799.3443066491</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>20415.1942539747</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>22162.4293594377</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>23559.5929886225</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>25233.9935329319</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>26258.6984077211</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>26823.0191954073</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1350.062</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1439.618</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>1411.799</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1373.275</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>1358.725</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>1327.363</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1294.99</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>1324.508</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>1341.431</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>1257.684</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>1306.669</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>1348.085</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>1335.895</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>1377.885</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>1330.287</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>1250.686</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>1216.328</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>1164.937</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>1140.684</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>1135.158</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>1101.667</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>1102.228</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>1125.446</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>1155.474</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>1260.274</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>1273.333</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>1346.784</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>13673.7089478468</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>13536.2340506829</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>14232.324083183</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>15419.524257846</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>16502.4574499901</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>16868.4449151554</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>19704.403059042</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>20021.8880271525</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>20704.8247292162</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>21946.7184291548</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>22838.6060144749</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>24318.8551194646</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>26879.6173211932</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>28938.3169381605</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>29225.1998416152</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>30373.7677583634</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>29829.91708192</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>29186.5285662523</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>30146.6510322244</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>30302.2136439727</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>31656.5198095324</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>32481.6865855105</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>34719.8665107995</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>36783.499845472</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>37352.3669762304</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>41299.0840447624</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>42481.5512373978</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>940.256</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1011.085</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>851.636</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>951.968</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>983.011</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>1038.45</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1104.238</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>962.968</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>1031.416</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>1109.189</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>1105.478</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>1153.072</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1057.227</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>1099.026</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>1155.466</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>1204.559</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>1101.053</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>1207.745</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>1102.849</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>953.421</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>1127.55</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>1000.027</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>1057.813</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>1222.127</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>1155.553</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>1544.762</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1271.795</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>58.23</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>22.36</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>43.81</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>20.72</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>13.61</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>14.71</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>25.32</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>23.83</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>20.15</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>22.11</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>22.99</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>30.63</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>29.42</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>-8.3</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-19.48</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-16.28</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>-22.26</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>-14.45</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>42.98</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>17.54</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>36.53</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>26.07</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12.85</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>23.72</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>-4.39</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>20.83</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>28.384</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>21.459</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>18.076</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>26.271</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>15.016</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>21.59</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>15.586</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>13.714</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>13.215</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>13.029</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>12.576</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>12.364</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>24176.323</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>11.329</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>56.635</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>77696.81</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>9.633</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>7.522</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>2267.287</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>2314.609</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>3668206.035</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>156.138</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>2611.512</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2696.141</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>2889.418</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2995.223</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>8175.81954320883</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>8840.3426975946</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>9953.24372100948</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>10857.9431929656</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>11689.8384949903</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>12326.8402589887</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>11110.3879649128</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>12648.9698477271</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>13897.7010523455</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>14603.025658787</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>15569.8471786047</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>17339.6570092905</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>19838.7954815658</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>21533.1917053494</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>19184.7225170397</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>18300.7030148071</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>19640.9158204364</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>19394.3744714304</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>18953.0151329618</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>19975.1111989552</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>20615.6604309082</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>22468.9343200254</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>23449.9080952164</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>25068.2486747675</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>27241.7650780668</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>25541.6992954747</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>26019.3656699751</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1487721296.88622</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1237153000.00049</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1224755999.99996</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1149185999.99967</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1116763000.00009</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1152636999.9992</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1266666000.0004</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1206750000.00013</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1277217000.00024</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1332742000.00008</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1349860000.00048</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1418119000.00051</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1381085000.00001</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1422378999.99977</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1059614999.99969</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>969944000.000027</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>921763999.999712</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>938904000.000226</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>943438999.999989</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1363228275.53633</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>1325300554.16544</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>1365311307.64343</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>1333554858.87187</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>1379206136.68971</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>1429647985.31091</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>1476889353.12059</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>1536761892.28104</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2232145630.96959</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2018980000.00052</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1996752000.00013</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1956223999.99966</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1979158999.9998</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1982422999.99998</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1976890000.00036</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1969298000.00018</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2009122999.99995</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1937166000.00002</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2020152000.00012</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2062407000.00022</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2053903000.00008</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2105926999.99977</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2066278999.99985</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1999600000.00011</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1959743999.99966</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1885166000.00019</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1865532999.99996</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1831860058.12441</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>1796069209.74435</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>1867297877.08137</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>1845664409.77999</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>1915772811.10684</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2034112412.62926</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>2103567832.18129</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>2220647798.48616</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1350062086.94366</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1439617552.23849</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1411799422.43922</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1373274744.34657</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1358724544.9178</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1327362765.59105</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1294989539.98814</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1324507573.57043</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1341430935.89152</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1257683639.47811</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1306668534.05806</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1348085071.69752</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1335894856.05969</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1377885375.39101</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1330286517.56478</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1250686343.82542</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1216327979.88867</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1164936847.9357</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1140684173.49504</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1135158261.54193</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>1101666531.96655</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>1102228174.58453</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>1125445808.10566</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>1155474315.76638</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>1260273893.87133</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>1273332607.38663</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1346784034.50052</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1133556.67817282</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>909299.999999969</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>899799.999999948</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>920300.000000011</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>927200.000000258</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>912700.000000097</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>919100.000000021</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>935200.000000061</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>945999.999999943</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>920400.000000075</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>965499.999999995</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>973800.000000009</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>985900.000000113</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1005900.00000013</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>991400.000000042</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>975099.999999875</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>962200.000000225</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>931500.000000102</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>918900.000000062</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>905652.792080042</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>889723.758863566</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>928335.306032193</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>919623.016102114</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>956117.545934962</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>1017403.4979944</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>1055242.41956138</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1117459.36428547</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>913205.35818361</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>758799.999999973</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>750999.999999982</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>752700.000000082</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>750900.000000314</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>746400.000000104</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>775800.000000032</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>779800.000000092</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>794899.999999991</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>795100.000000044</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>816700.000000017</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>829900.000000008</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>830100.000000113</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>850700.00000012</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>851200.000000046</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>816899.999999904</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>795700.000000219</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>774500.000000136</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>769300.000000015</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>755347.568254849</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>738853.06707971</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>765748.083060304</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>757196.391815487</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>790182.563245238</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>823918.391262486</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>859646.403734855</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>907539.863673011</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2232145630.96959</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2018980000.00052</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1996752000.00013</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1956223999.99966</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1979158999.9998</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1982422999.99998</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1976890000.00036</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1969298000.00018</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2009122999.99995</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1937166000.00002</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2020152000.00012</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2062407000.00022</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2053903000.00008</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2105926999.99977</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2066278999.99985</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1999600000.00011</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1959743999.99966</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1885166000.00019</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1865532999.99996</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1831860058.12441</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>1796069209.74435</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>1867297877.08137</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>1845664409.77999</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>1915772811.10684</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2034112412.62926</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>2103567832.18129</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2220647798.48616</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1487721296.88622</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1237153000.00049</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1224755999.99996</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1149185999.99967</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1116763000.00009</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1152636999.9992</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1266666000.0004</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1206750000.00013</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1277217000.00024</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1332742000.00008</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1349860000.00048</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1418119000.00051</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1381085000.00001</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1422378999.99977</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1059614999.99969</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>969944000.000027</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>921763999.999712</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>938904000.000226</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>943438999.999989</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1363228275.53633</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>1325300554.16544</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>1365311307.64343</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>1333554858.87187</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>1379206136.68971</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>1429647985.31091</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>1476889353.12059</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1536761892.28104</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>43409.5182216802</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>45490.9502312238</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>49555.6591750823</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>53027.4736195216</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>56349.4629836537</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>58999.4606835631</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>62618.4265991279</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>66487.110253563</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>70047.3846787467</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>74083.5086087158</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>79423.0891551823</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>86426.2615947887</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>98887.9440806878</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>105386.498827615</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>96582.5803046021</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>98683.4628215453</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>103367.311644521</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>101020.506110679</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>101130.194071432</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>102335.974460575</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>107159.87672243</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>111364.12598335</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>120236.334284877</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>128186.869836628</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>135916.527471233</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>142880.163957492</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>142183.724434606</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>14831.1094244595</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>15005.4371222249</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>15825.4915711832</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>16942.7648175216</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>18290.973388081</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>18576.8355911716</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>21694.9017777977</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>22303.7223234667</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>22948.2889613731</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>24311.7081870474</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>25319.5712679449</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>26831.1516460032</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>29380.114346924</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>31494.2939983561</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>31516.0138866074</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>32700.7525994904</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>32332.1590671182</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>31517.8419814692</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>32227.9588782521</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>32808.1829661015</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>33924.0432499866</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>34291.5571627396</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>36938.7698136963</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>39333.2821353173</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>40724.488061406</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>44421.6907605218</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>45808.4534376981</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
